--- a/videos_casla.xlsx
+++ b/videos_casla.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\VOLEY CASLA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108F67C5-9403-4322-B4E1-CF3AFDE276E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6B12E4-DF2F-4C8D-9392-3AC053493626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="744" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="744" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIXTURE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3021" uniqueCount="234">
   <si>
     <t>CALENDARIO — el sistema agarra solo el próximo rival según la fecha de hoy</t>
   </si>
@@ -716,6 +716,24 @@
   </si>
   <si>
     <t>https://youtu.be/CkiCDzs7EOk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/dxdCIr4P2Uo</t>
+  </si>
+  <si>
+    <t>https://youtu.be/q7gJEGjJS38</t>
+  </si>
+  <si>
+    <t>https://youtu.be/BjI8WAnIgLs</t>
+  </si>
+  <si>
+    <t>https://youtu.be/4M6a692QuS0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/o0gKXn7L1Xc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/1_JOBvX1dIk</t>
   </si>
 </sst>
 </file>
@@ -6758,7 +6776,9 @@
       <c r="E10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="4"/>
+      <c r="F10" s="4" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
@@ -6938,7 +6958,9 @@
       <c r="E20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
@@ -7028,7 +7050,9 @@
       <c r="E25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F25" s="4"/>
+      <c r="F25" s="4" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -7046,7 +7070,9 @@
       <c r="E26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
@@ -7208,7 +7234,9 @@
       <c r="E35" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F35" s="4"/>
+      <c r="F35" s="4" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
@@ -7568,7 +7596,9 @@
       <c r="E55" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F55" s="4"/>
+      <c r="F55" s="4" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">

--- a/videos_casla.xlsx
+++ b/videos_casla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\VOLEY CASLA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6B12E4-DF2F-4C8D-9392-3AC053493626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE3A693-9647-461D-940C-9C2BE7051B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="744" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="744" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIXTURE" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,12 @@
     <sheet name="UBA" sheetId="12" r:id="rId12"/>
     <sheet name="Campana" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3021" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3028" uniqueCount="241">
   <si>
     <t>CALENDARIO — el sistema agarra solo el próximo rival según la fecha de hoy</t>
   </si>
@@ -734,6 +734,27 @@
   </si>
   <si>
     <t>https://youtu.be/1_JOBvX1dIk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/YtymKWJxlz8</t>
+  </si>
+  <si>
+    <t>https://youtu.be/laLGmdhPxag</t>
+  </si>
+  <si>
+    <t>https://youtu.be/kid4dFwa3nk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/li3wHl6oUHc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/WukBdaCIaWw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fM7do21k0ns</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ohWOCGNrOos</t>
   </si>
 </sst>
 </file>
@@ -7762,7 +7783,9 @@
       <c r="E2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="4" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -8284,7 +8307,9 @@
       <c r="E31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="4"/>
+      <c r="F31" s="4" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
@@ -8446,7 +8471,9 @@
       <c r="E40" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F40" s="4"/>
+      <c r="F40" s="4" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
@@ -8734,7 +8761,9 @@
       <c r="E56" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F56" s="4"/>
+      <c r="F56" s="4" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
@@ -8842,7 +8871,9 @@
       <c r="E62" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F62" s="4"/>
+      <c r="F62" s="4" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
@@ -8914,7 +8945,9 @@
       <c r="E66" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F66" s="4"/>
+      <c r="F66" s="4" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
@@ -8932,7 +8965,9 @@
       <c r="E67" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F67" s="4"/>
+      <c r="F67" s="4" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
